--- a/conditions/male_stimuli.xlsx
+++ b/conditions/male_stimuli.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrikhrabanek/Desktop/from_work_mac/Study_1/PsychoPy_experiment/creaky_experiment/conditions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pahr0811/Documents/PhD/Year_1/Study_1/female_first_experiment/Vocal Fry Experiment #2/conditions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF86C863-3E1B-5441-9F00-15892CA3CDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A5A687-1332-2A43-9E7F-1E43999C5572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="29040" windowHeight="17640" xr2:uid="{E94A0D02-C4AD-45DA-9BE1-25E231290689}"/>
+    <workbookView xWindow="10280" yWindow="2260" windowWidth="32920" windowHeight="22140" xr2:uid="{E94A0D02-C4AD-45DA-9BE1-25E231290689}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,136 +38,136 @@
     <t>stimFile</t>
   </si>
   <si>
-    <t>stimuli_f0/tad_m_c2_p2_h-2_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_m_c-1_p-3_h-3_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_m_c-1_p1_h3_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_m_c0_p-2_h3_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_m_c0_p0_h-3_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_m_c1_p-3_h-3_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_m_c1_p2_h-2_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_m_c2_p-3_h-1_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_m_c2_p-3_h-3_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_m_c2_p0_h2_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_m_c2_p2_h-2_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/hab_m_c2_p2_h1_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_m_c-1_p3_h3_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_m_c-2_p2_h-2_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_m_c-2_p3_h0_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_m_c0_p1_h3_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_m_c1_p-1_h-3_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_m_c1_p1_h2_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_m_c1_p3_h-3_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_m_c2_p-2_h-3_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_m_c2_p-3_h2_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_m_c2_p2_h1_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/had_m_c2_p2_h3_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_m_c-1_p-3_h3_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_m_c-1_p0_h3_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_m_c0_p-1_h-2_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_m_c0_p-1_h-3_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_m_c0_p0_h-1_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_m_c0_p0_h-1_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_m_c1_p-2_h-2_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_m_c2_p-1_h-3_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_m_c2_p0_h3_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_m_c2_p1_h-2_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tab_m_c2_p2_h3_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_m_c-1_p-3_h-3_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_m_c-1_p3_h1_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_m_c0_p-1_h-1_r1.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_m_c0_p-2_h1_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_m_c0_p0_h1_r2.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_m_c0_p3_h-1_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_m_c1_p-2_h1_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_m_c1_p0_h2_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_m_c1_p2_h-2_r3.wav</t>
-  </si>
-  <si>
-    <t>stimuli_f0/tad_m_c2_p-1_h2_r3.wav</t>
+    <t>stimuli/dab_m_c-1_p-1_h3_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_m_c-1_p1_h-3_r1.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_m_c-1_p1_h0_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_m_c-2_p-3_h-3_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_m_c-2_p0_h-3_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_m_c-2_p1_h-3_r1.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_m_c1_p-2_h2_r2.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_m_c2_p0_h3_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_m_c2_p1_h-2_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_m_c2_p3_h-3_r1.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dab_m_c2_p3_h0_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_m_c-1_p0_h-2_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_m_c-1_p0_h3_r2.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_m_c-2_p-1_h0_r2.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_m_c-2_p-1_h3_r2.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_m_c-2_p1_h1_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_m_c0_p-2_h0_r2.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_m_c0_p-3_h2_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_m_c1_p-3_h-2_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_m_c2_p-1_h1_r2.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_m_c2_p-2_h1_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/dad_m_c2_p3_h2_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_m_c-1_p-1_h2_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_m_c-1_p-2_h-1_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_m_c-1_p-2_h-3_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_m_c-1_p0_h3_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_m_c-2_p-1_h-3_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_m_c-2_p-2_h2_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_m_c-2_p-3_h-3_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_m_c-2_p0_h-3_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_m_c0_p1_h3_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_m_c1_p0_h-1_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tab_m_c2_p-3_h-1_r2.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_m_c-1_p-3_h-2_r1.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_m_c-1_p0_h3_r1.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_m_c-2_p-2_h-2_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_m_c-2_p-2_h1_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_m_c0_p-3_h-3_r1.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_m_c0_p3_h-1_r3.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_m_c1_p-2_h-3_r2.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_m_c1_p-2_h-3_r5.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_m_c1_p2_h1_r1.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_m_c1_p2_h3_r4.wav</t>
+  </si>
+  <si>
+    <t>stimuli/tad_m_c2_p-2_h-2_r3.wav</t>
   </si>
 </sst>
 </file>
@@ -1054,6 +1054,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="805e3853-2971-4830-a200-7929f1998a0d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="1abb6105-976e-4641-94d5-932be0f0089d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100281F5302C0C8424184A8BFB4F64AD156" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a7dddae9028d61b06595b7475003a62f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="805e3853-2971-4830-a200-7929f1998a0d" xmlns:ns3="1abb6105-976e-4641-94d5-932be0f0089d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd95256a0d3ea48f6d8d5ce446b80fb5" ns2:_="" ns3:_="">
     <xsd:import namespace="805e3853-2971-4830-a200-7929f1998a0d"/>
@@ -1242,17 +1253,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="805e3853-2971-4830-a200-7929f1998a0d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="1abb6105-976e-4641-94d5-932be0f0089d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C198A863-1F77-4B90-9B7E-D9A5CE4D14B1}">
   <ds:schemaRefs>
@@ -1262,6 +1262,19 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E8FE25B-F2A6-404B-BFAA-4FDF41C79620}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="10c3a147-0d64-46aa-a281-dc97358e8373"/>
+    <ds:schemaRef ds:uri="d7532cd0-e888-47d6-8f58-db0210f25002"/>
+    <ds:schemaRef ds:uri="805e3853-2971-4830-a200-7929f1998a0d"/>
+    <ds:schemaRef ds:uri="1abb6105-976e-4641-94d5-932be0f0089d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6E047D9-D247-4E2D-8E73-39594A3DD58C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1280,15 +1293,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E8FE25B-F2A6-404B-BFAA-4FDF41C79620}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="10c3a147-0d64-46aa-a281-dc97358e8373"/>
-    <ds:schemaRef ds:uri="d7532cd0-e888-47d6-8f58-db0210f25002"/>
-    <ds:schemaRef ds:uri="805e3853-2971-4830-a200-7929f1998a0d"/>
-    <ds:schemaRef ds:uri="1abb6105-976e-4641-94d5-932be0f0089d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{35b66c34-d3f7-4b74-a2f5-5e46d77d2b05}" enabled="1" method="Privileged" siteId="{1e586649-7317-42fb-8949-66923d34ba7e}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>